--- a/test_samples/EXPRESS_MAXIMUM/sample3_ref.xlsx
+++ b/test_samples/EXPRESS_MAXIMUM/sample3_ref.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PT. EXPRESS MAXIMUM</t>
+          <t>PT.EXPRESS MAXIMUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/test_samples/EXPRESS_MAXIMUM/sample3_ref.xlsx
+++ b/test_samples/EXPRESS_MAXIMUM/sample3_ref.xlsx
@@ -543,7 +543,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1023,7 +1023,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
